--- a/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0001.xlsx
@@ -21977,7 +21977,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Lấy lại Thiết bị Điều Chỉnh và bắt đầu Điều Chỉnh.</t>
+          <t>Lấy lại Thiết bị Modulation và bắt đầu Modulation.</t>
         </is>
       </c>
     </row>
@@ -27307,7 +27307,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Dùng Sensor để tìm manh mối quanh Hội Trường Điều Chỉnh</t>
+          <t>Dùng Sensor để tìm manh mối quanh Hội Trường Modulation</t>
         </is>
       </c>
     </row>
